--- a/videos/organization.xlsx
+++ b/videos/organization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/videos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="894" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DB3F2E8-4BA8-4ED0-A77A-8A086F288B7C}"/>
+  <xr:revisionPtr revIDLastSave="896" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB8FCF5E-E7A1-4AC3-9ADD-1D82DC6B9946}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9669,7 +9669,7 @@
       <c r="T14" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="U14" s="14" t="s">
+      <c r="U14" s="13" t="s">
         <v>969</v>
       </c>
       <c r="V14" s="14" t="s">
@@ -9903,7 +9903,7 @@
       <c r="T16" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="U16" s="14" t="s">
+      <c r="U16" s="13" t="s">
         <v>971</v>
       </c>
       <c r="V16" s="14" t="s">
@@ -15051,6 +15051,8 @@
     <hyperlink ref="U31" r:id="rId3" xr:uid="{FED77476-3F3B-4268-ADD6-760E3385FC38}"/>
     <hyperlink ref="U45" r:id="rId4" xr:uid="{876472B8-425C-44AE-9B8F-7C9E6ED5E9E1}"/>
     <hyperlink ref="U2" r:id="rId5" xr:uid="{B58C7C2F-2F3D-427D-87BF-2D146F134BD9}"/>
+    <hyperlink ref="U14" r:id="rId6" xr:uid="{23023A60-E45D-4B07-ACA9-1EF6705CC980}"/>
+    <hyperlink ref="U16" r:id="rId7" xr:uid="{D9EB504E-8F69-4332-A9E2-F5D1CEBA8B71}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/videos/organization.xlsx
+++ b/videos/organization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/videos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="896" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB8FCF5E-E7A1-4AC3-9ADD-1D82DC6B9946}"/>
+  <xr:revisionPtr revIDLastSave="898" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D29B70-62D2-488C-BA45-48DF5415F6A1}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12009,7 +12009,7 @@
       <c r="T34" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="U34" s="14" t="s">
+      <c r="U34" s="13" t="s">
         <v>947</v>
       </c>
       <c r="V34" s="14" t="s">
@@ -12126,7 +12126,7 @@
       <c r="T35" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="U35" s="14" t="s">
+      <c r="U35" s="13" t="s">
         <v>974</v>
       </c>
       <c r="V35" s="14" t="s">
@@ -15053,6 +15053,8 @@
     <hyperlink ref="U2" r:id="rId5" xr:uid="{B58C7C2F-2F3D-427D-87BF-2D146F134BD9}"/>
     <hyperlink ref="U14" r:id="rId6" xr:uid="{23023A60-E45D-4B07-ACA9-1EF6705CC980}"/>
     <hyperlink ref="U16" r:id="rId7" xr:uid="{D9EB504E-8F69-4332-A9E2-F5D1CEBA8B71}"/>
+    <hyperlink ref="U34" r:id="rId8" xr:uid="{0E499D0D-1749-4E05-B850-2D0F77BBE5FF}"/>
+    <hyperlink ref="U35" r:id="rId9" xr:uid="{B6ED1C37-5C44-45F0-8AE7-720FBF9292F0}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/videos/organization.xlsx
+++ b/videos/organization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/videos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="898" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D29B70-62D2-488C-BA45-48DF5415F6A1}"/>
+  <xr:revisionPtr revIDLastSave="904" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C3F277-A932-4DC7-8DA6-4EA649CAF3E0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3114" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3114" uniqueCount="1116">
   <si>
     <t>Indicador</t>
   </si>
@@ -4022,6 +4022,12 @@
   </si>
   <si>
     <t>Projetos em que o campo Saídas difere da soma dos canais</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/pulse/apply-vs-npselect-pandas-uma-an%C3%A1lise-quantitativa-de-santos-pereira-0u32f/?trackingId=7PoWseq%2BSxi1JMzABWt3FA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/ozsp12_apply-vs-npselect-no-pandas-uma-an%C3%A1lise-activity-7394895580038238208-vA47?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAYVLuwBRoOGLctydlL6oZP7Ffwirgxbs9Q</t>
   </si>
 </sst>
 </file>
@@ -4556,7 +4562,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>4</c:v>
@@ -4910,10 +4916,10 @@
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -6587,27 +6593,27 @@
       <c r="B5" s="21"/>
       <c r="C5" s="20">
         <f>SUM(Matriz!$AE$2:$AE$60)</f>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="20">
         <f>SUM(Matriz!$AF$2:$AF$60)</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" s="21"/>
       <c r="G5" s="22">
         <f>IFERROR($C$5/($A$5*12),0)</f>
-        <v>0.19680851063829788</v>
+        <v>0.20035460992907803</v>
       </c>
       <c r="H5" s="21"/>
       <c r="I5" s="23">
         <f>IFERROR($C$5/$A$5,0)</f>
-        <v>2.3617021276595747</v>
+        <v>2.4042553191489362</v>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="20">
         <f>COUNTIF(Matriz!$AE$2:$AE$60,"&gt;=3")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="21"/>
       <c r="M5" s="17"/>
@@ -6672,7 +6678,7 @@
       <c r="F8" s="21"/>
       <c r="G8" s="20">
         <f>COUNTIF($H$12:$H$23,"&gt;0")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="20">
@@ -6980,15 +6986,15 @@
       </c>
       <c r="H17" s="27">
         <f>SUM(INDEX(Matriz!$F$2:$Q$60,0,MATCH($G17,Matriz!$F$1:$Q$1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="27">
         <f>COUNTIF(INDEX(Matriz!$R$2:$AC$60,0,MATCH($G17&amp;" (link)",Matriz!$R$1:$AC$1,0)),"http*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.1276595744680851E-2</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -7020,15 +7026,15 @@
       </c>
       <c r="H18" s="27">
         <f>SUM(INDEX(Matriz!$F$2:$Q$60,0,MATCH($G18,Matriz!$F$1:$Q$1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="27">
         <f>COUNTIF(INDEX(Matriz!$R$2:$AC$60,0,MATCH($G18&amp;" (link)",Matriz!$R$1:$AC$1,0)),"http*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.1276595744680851E-2</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
@@ -7120,7 +7126,7 @@
       </c>
       <c r="B21" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A21,Matriz!$AE$2:$AE$60)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C21" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A21,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -7128,11 +7134,11 @@
       </c>
       <c r="D21" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A21,Matriz!$AF$2:$AF$60)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="26" t="s">
@@ -7240,7 +7246,7 @@
       </c>
       <c r="B24" s="30">
         <f>SUM($B$12:$B$23)</f>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C24" s="30">
         <f>SUM($C$12:$C$23)</f>
@@ -7248,11 +7254,11 @@
       </c>
       <c r="D24" s="30">
         <f>SUM($D$12:$D$23)</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E24" s="31">
         <f>IFERROR($B$24/($C$24*12),0)</f>
-        <v>0.19680851063829788</v>
+        <v>0.20035460992907803</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="29" t="s">
@@ -7260,15 +7266,15 @@
       </c>
       <c r="H24" s="30">
         <f>SUM($H$12:$H$23)</f>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I24" s="30">
         <f>SUM($I$12:$I$23)</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J24" s="31">
         <f>IFERROR($H$24/($A$5*12),0)</f>
-        <v>0.19680851063829788</v>
+        <v>0.20035460992907803</v>
       </c>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
@@ -7410,13 +7416,13 @@
     <row r="30" spans="1:13">
       <c r="A30" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A30),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Fluid dynamics in the warp drive spacetime geometry</v>
+        <v>Teste de complexidade temporal do método select (numpy) vs apply (pandas)</v>
       </c>
       <c r="B30" s="26"/>
       <c r="C30" s="26"/>
       <c r="D30" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$B$2:$B$60,MATCH(ROWS($A$28:$A30),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Warp Drive</v>
+        <v>Programação</v>
       </c>
       <c r="E30" s="27">
         <f>IFERROR(INDEX(Matriz!$AE$2:$AE$60,MATCH(ROWS($A$28:$A30),Matriz!$AH$2:$AH$60,0)),"")</f>
@@ -7424,7 +7430,7 @@
       </c>
       <c r="F30" s="27">
         <f>IFERROR(INDEX(Matriz!$AF$2:$AF$60,MATCH(ROWS($A$28:$A30),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="28">
         <f t="shared" si="2"/>
@@ -7445,7 +7451,7 @@
     <row r="31" spans="1:13">
       <c r="A31" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A31),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Charged dust solutions for the warp drive spacetime</v>
+        <v>Fluid dynamics in the warp drive spacetime geometry</v>
       </c>
       <c r="B31" s="26"/>
       <c r="C31" s="26"/>
@@ -7480,7 +7486,7 @@
     <row r="32" spans="1:13">
       <c r="A32" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A32),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Perfect fluid warp drive solutions with the cosmological constant</v>
+        <v>Charged dust solutions for the warp drive spacetime</v>
       </c>
       <c r="B32" s="26"/>
       <c r="C32" s="26"/>
@@ -7515,7 +7521,7 @@
     <row r="33" spans="1:13">
       <c r="A33" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A33),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Warp drive dynamic solutions considering different fluid sources</v>
+        <v>Perfect fluid warp drive solutions with the cosmological constant</v>
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
@@ -7550,7 +7556,7 @@
     <row r="34" spans="1:13">
       <c r="A34" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A34),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Matching the Alcubierre and Minkowski spacetimes.</v>
+        <v>Warp drive dynamic solutions considering different fluid sources</v>
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="26"/>
@@ -7585,7 +7591,7 @@
     <row r="35" spans="1:13">
       <c r="A35" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A35),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Dust content content solutions for the Alcubierre warp drive spacetime.</v>
+        <v>Matching the Alcubierre and Minkowski spacetimes.</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
@@ -7595,7 +7601,7 @@
       </c>
       <c r="E35" s="27">
         <f>IFERROR(INDEX(Matriz!$AE$2:$AE$60,MATCH(ROWS($A$28:$A35),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="27">
         <f>IFERROR(INDEX(Matriz!$AF$2:$AF$60,MATCH(ROWS($A$28:$A35),Matriz!$AH$2:$AH$60,0)),"")</f>
@@ -7603,7 +7609,7 @@
       </c>
       <c r="G35" s="28">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="26" t="s">
@@ -7620,25 +7626,25 @@
     <row r="36" spans="1:13">
       <c r="A36" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Resolvendo equação polinomial de quarta ordem e demonstrando um teorema de redução de ordem</v>
+        <v>Dust content content solutions for the Alcubierre warp drive spacetime.</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
       <c r="D36" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$B$2:$B$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Álgebra</v>
+        <v>Warp Drive</v>
       </c>
       <c r="E36" s="27">
         <f>IFERROR(INDEX(Matriz!$AE$2:$AE$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="27">
         <f>IFERROR(INDEX(Matriz!$AF$2:$AF$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="28">
         <f t="shared" si="2"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="26" t="s">
@@ -7655,7 +7661,7 @@
     <row r="37" spans="1:13">
       <c r="A37" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A37),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Resolvendo (polinômios): x³ + px + q é divisível por (x-a)², encontre a relação entre p e q.</v>
+        <v>Resolvendo equação polinomial de quarta ordem e demonstrando um teorema de redução de ordem</v>
       </c>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -8306,7 +8312,7 @@
       </c>
       <c r="AH2" s="4">
         <f>IF($C2="","",RANK($AG2,$AG$2:$AG$60))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI2" s="4">
         <f>IF($C2="","",MAX(0,$AE2-$AF2))</f>
@@ -8423,7 +8429,7 @@
       </c>
       <c r="AH3" s="4">
         <f t="shared" ref="AH3:AH60" si="3">IF($C3="","",RANK($AG3,$AG$2:$AG$60))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI3" s="4">
         <f t="shared" ref="AI3:AI60" si="4">IF($C3="","",MAX(0,$AE3-$AF3))</f>
@@ -8540,7 +8546,7 @@
       </c>
       <c r="AH4" s="4">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI4" s="4">
         <f t="shared" si="4"/>
@@ -8657,7 +8663,7 @@
       </c>
       <c r="AH5" s="4">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI5" s="4">
         <f t="shared" si="4"/>
@@ -8774,7 +8780,7 @@
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="4"/>
@@ -8891,7 +8897,7 @@
       </c>
       <c r="AH7" s="4">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="4"/>
@@ -9008,7 +9014,7 @@
       </c>
       <c r="AH8" s="4">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8" s="4">
         <f t="shared" si="4"/>
@@ -9125,7 +9131,7 @@
       </c>
       <c r="AH9" s="4">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI9" s="4">
         <f t="shared" si="4"/>
@@ -9242,7 +9248,7 @@
       </c>
       <c r="AH10" s="4">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI10" s="4">
         <f t="shared" si="4"/>
@@ -9359,7 +9365,7 @@
       </c>
       <c r="AH11" s="4">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI11" s="4">
         <f t="shared" si="4"/>
@@ -9476,7 +9482,7 @@
       </c>
       <c r="AH12" s="4">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="4"/>
@@ -9593,7 +9599,7 @@
       </c>
       <c r="AH13" s="4">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="4"/>
@@ -9710,7 +9716,7 @@
       </c>
       <c r="AH14" s="4">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="4"/>
@@ -9827,7 +9833,7 @@
       </c>
       <c r="AH15" s="4">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="4"/>
@@ -9944,7 +9950,7 @@
       </c>
       <c r="AH16" s="4">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="4"/>
@@ -10295,7 +10301,7 @@
       </c>
       <c r="AH19" s="4">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="4"/>
@@ -10412,7 +10418,7 @@
       </c>
       <c r="AH20" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="4"/>
@@ -10529,7 +10535,7 @@
       </c>
       <c r="AH21" s="4">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="4"/>
@@ -10646,7 +10652,7 @@
       </c>
       <c r="AH22" s="4">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="4"/>
@@ -10763,7 +10769,7 @@
       </c>
       <c r="AH23" s="4">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="4"/>
@@ -10880,7 +10886,7 @@
       </c>
       <c r="AH24" s="4">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="4"/>
@@ -10997,7 +11003,7 @@
       </c>
       <c r="AH25" s="4">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="4"/>
@@ -11114,7 +11120,7 @@
       </c>
       <c r="AH26" s="4">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="4"/>
@@ -11231,7 +11237,7 @@
       </c>
       <c r="AH27" s="4">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="4"/>
@@ -11348,7 +11354,7 @@
       </c>
       <c r="AH28" s="4">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="4"/>
@@ -11465,7 +11471,7 @@
       </c>
       <c r="AH29" s="4">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="4"/>
@@ -11582,7 +11588,7 @@
       </c>
       <c r="AH30" s="4">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="4"/>
@@ -11699,7 +11705,7 @@
       </c>
       <c r="AH31" s="4">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="4"/>
@@ -11816,7 +11822,7 @@
       </c>
       <c r="AH32" s="4">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="4"/>
@@ -11933,7 +11939,7 @@
       </c>
       <c r="AH33" s="4">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="4"/>
@@ -12050,7 +12056,7 @@
       </c>
       <c r="AH34" s="4">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AI34" s="4">
         <f t="shared" si="4"/>
@@ -12097,10 +12103,10 @@
         <v>1</v>
       </c>
       <c r="K35" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="11">
         <v>0</v>
@@ -12132,11 +12138,11 @@
       <c r="V35" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="W35" s="14" t="s">
-        <v>1083</v>
-      </c>
-      <c r="X35" s="14" t="s">
-        <v>1083</v>
+      <c r="W35" s="13" t="s">
+        <v>1115</v>
+      </c>
+      <c r="X35" s="13" t="s">
+        <v>1114</v>
       </c>
       <c r="Y35" s="14" t="s">
         <v>1083</v>
@@ -12155,19 +12161,19 @@
       </c>
       <c r="AE35" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF35" s="4">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG35" s="4">
         <f t="shared" si="2"/>
-        <v>2966</v>
+        <v>4966</v>
       </c>
       <c r="AH35" s="4">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="AI35" s="4">
         <f t="shared" si="4"/>
@@ -12518,7 +12524,7 @@
       </c>
       <c r="AH38" s="4">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="4"/>
@@ -12635,7 +12641,7 @@
       </c>
       <c r="AH39" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI39" s="4">
         <f t="shared" si="4"/>
@@ -12752,7 +12758,7 @@
       </c>
       <c r="AH40" s="4">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="4"/>
@@ -12869,7 +12875,7 @@
       </c>
       <c r="AH41" s="4">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="4"/>
@@ -12986,7 +12992,7 @@
       </c>
       <c r="AH42" s="4">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="4"/>
@@ -13103,7 +13109,7 @@
       </c>
       <c r="AH43" s="4">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="4"/>
@@ -15055,6 +15061,8 @@
     <hyperlink ref="U16" r:id="rId7" xr:uid="{D9EB504E-8F69-4332-A9E2-F5D1CEBA8B71}"/>
     <hyperlink ref="U34" r:id="rId8" xr:uid="{0E499D0D-1749-4E05-B850-2D0F77BBE5FF}"/>
     <hyperlink ref="U35" r:id="rId9" xr:uid="{B6ED1C37-5C44-45F0-8AE7-720FBF9292F0}"/>
+    <hyperlink ref="W35" r:id="rId10" xr:uid="{5ADC2036-8BE3-4C29-9211-776990B2FA5B}"/>
+    <hyperlink ref="X35" r:id="rId11" xr:uid="{7B97F0CB-76D2-4A95-B897-486B43CC99C3}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/videos/organization.xlsx
+++ b/videos/organization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/videos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="904" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C3F277-A932-4DC7-8DA6-4EA649CAF3E0}"/>
+  <xr:revisionPtr revIDLastSave="914" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20323B6F-6C3F-4A48-B8B1-71F4FF39C15E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Periódicos" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Matriz!$A$1:$AC$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Matriz!$A$1:$AC$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Periódicos!$A$1:$N$168</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -4535,40 +4535,40 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>27</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4925,7 +4925,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6593,7 +6593,7 @@
       <c r="B5" s="21"/>
       <c r="C5" s="20">
         <f>SUM(Matriz!$AE$2:$AE$60)</f>
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="20">
@@ -6603,17 +6603,17 @@
       <c r="F5" s="21"/>
       <c r="G5" s="22">
         <f>IFERROR($C$5/($A$5*12),0)</f>
-        <v>0.20035460992907803</v>
+        <v>0.26950354609929078</v>
       </c>
       <c r="H5" s="21"/>
       <c r="I5" s="23">
         <f>IFERROR($C$5/$A$5,0)</f>
-        <v>2.4042553191489362</v>
+        <v>3.2340425531914891</v>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="20">
         <f>COUNTIF(Matriz!$AE$2:$AE$60,"&gt;=3")</f>
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="L5" s="21"/>
       <c r="M5" s="17"/>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="B12" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A12,Matriz!$AE$2:$AE$60)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A12,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="E12" s="28">
         <f>IFERROR($B12/($C12*12),0)</f>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="26" t="s">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="B13" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A13,Matriz!$AE$2:$AE$60)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A13,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13:E23" si="0">IFERROR($B13/($C13*12),0)</f>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="26" t="s">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B14" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A14,Matriz!$AE$2:$AE$60)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A14,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="E14" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="26" t="s">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="B15" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A15,Matriz!$AE$2:$AE$60)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C15" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A15,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="E15" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="26" t="s">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="B16" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A16,Matriz!$AE$2:$AE$60)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A16,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="E16" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="26" t="s">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B17" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A17,Matriz!$AE$2:$AE$60)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A17,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E17" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="26" t="s">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="B18" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A18,Matriz!$AE$2:$AE$60)</f>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C18" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A18,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="E18" s="28">
         <f t="shared" si="0"/>
-        <v>0.21666666666666667</v>
+        <v>0.28333333333333333</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="26" t="s">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B19" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A19,Matriz!$AE$2:$AE$60)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A19,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E19" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="26" t="s">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B20" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A20,Matriz!$AE$2:$AE$60)</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C20" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A20,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="E20" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="26" t="s">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="H20" s="27">
         <f>SUM(INDEX(Matriz!$F$2:$Q$60,0,MATCH($G20,Matriz!$F$1:$Q$1,0)))</f>
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="I20" s="27">
         <f>COUNTIF(INDEX(Matriz!$R$2:$AC$60,0,MATCH($G20&amp;" (link)",Matriz!$R$1:$AC$1,0)),"http*")</f>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="J20" s="28">
         <f t="shared" si="1"/>
-        <v>0.14893617021276595</v>
+        <v>0.97872340425531912</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="B21" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A21,Matriz!$AE$2:$AE$60)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A21,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="E21" s="28">
         <f t="shared" si="0"/>
-        <v>0.22222222222222221</v>
+        <v>0.30555555555555558</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="26" t="s">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="B22" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A22,Matriz!$AE$2:$AE$60)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A22,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="E22" s="28">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="26" t="s">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B23" s="27">
         <f>SUMIF(Matriz!$B$2:$B$60,$A23,Matriz!$AE$2:$AE$60)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" s="27">
         <f>COUNTIFS(Matriz!$B$2:$B$60,$A23,Matriz!$C$2:$C$60,"&lt;&gt;")</f>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="E23" s="28">
         <f t="shared" si="0"/>
-        <v>0.28125</v>
+        <v>0.30208333333333331</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="26" t="s">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="B24" s="30">
         <f>SUM($B$12:$B$23)</f>
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="C24" s="30">
         <f>SUM($C$12:$C$23)</f>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="E24" s="31">
         <f>IFERROR($B$24/($C$24*12),0)</f>
-        <v>0.20035460992907803</v>
+        <v>0.26950354609929078</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="29" t="s">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="H24" s="30">
         <f>SUM($H$12:$H$23)</f>
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="I24" s="30">
         <f>SUM($I$12:$I$23)</f>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="J24" s="31">
         <f>IFERROR($H$24/($A$5*12),0)</f>
-        <v>0.20035460992907803</v>
+        <v>0.26950354609929078</v>
       </c>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
@@ -7381,17 +7381,17 @@
     <row r="29" spans="1:13">
       <c r="A29" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A29),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Experimento de medição da densidade da água</v>
+        <v>Teste de complexidade temporal do método select (numpy) vs apply (pandas)</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
       <c r="D29" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$B$2:$B$60,MATCH(ROWS($A$28:$A29),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Física Clássica</v>
+        <v>Programação</v>
       </c>
       <c r="E29" s="27">
         <f>IFERROR(INDEX(Matriz!$AE$2:$AE$60,MATCH(ROWS($A$28:$A29),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="27">
         <f>IFERROR(INDEX(Matriz!$AF$2:$AF$60,MATCH(ROWS($A$28:$A29),Matriz!$AH$2:$AH$60,0)),"")</f>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G29" s="28">
         <f t="shared" ref="G29:G37" si="2">IFERROR($E29/12,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="26" t="s">
@@ -7416,13 +7416,13 @@
     <row r="30" spans="1:13">
       <c r="A30" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A30),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Teste de complexidade temporal do método select (numpy) vs apply (pandas)</v>
+        <v>Experimento de medição da densidade da água</v>
       </c>
       <c r="B30" s="26"/>
       <c r="C30" s="26"/>
       <c r="D30" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$B$2:$B$60,MATCH(ROWS($A$28:$A30),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Programação</v>
+        <v>Física Clássica</v>
       </c>
       <c r="E30" s="27">
         <f>IFERROR(INDEX(Matriz!$AE$2:$AE$60,MATCH(ROWS($A$28:$A30),Matriz!$AH$2:$AH$60,0)),"")</f>
@@ -7626,13 +7626,13 @@
     <row r="36" spans="1:13">
       <c r="A36" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Dust content content solutions for the Alcubierre warp drive spacetime.</v>
+        <v>Resolvendo equação polinomial de quarta ordem e demonstrando um teorema de redução de ordem</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
       <c r="D36" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$B$2:$B$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Warp Drive</v>
+        <v>Álgebra</v>
       </c>
       <c r="E36" s="27">
         <f>IFERROR(INDEX(Matriz!$AE$2:$AE$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="F36" s="27">
         <f>IFERROR(INDEX(Matriz!$AF$2:$AF$60,MATCH(ROWS($A$28:$A36),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="28">
         <f t="shared" si="2"/>
@@ -7661,7 +7661,7 @@
     <row r="37" spans="1:13">
       <c r="A37" s="26" t="str">
         <f>IFERROR(INDEX(Matriz!$C$2:$C$60,MATCH(ROWS($A$28:$A37),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>Resolvendo equação polinomial de quarta ordem e demonstrando um teorema de redução de ordem</v>
+        <v>Resolvendo (polinômios): x³ + px + q é divisível por (x-a)², encontre a relação entre p e q.</v>
       </c>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E37" s="27">
         <f>IFERROR(INDEX(Matriz!$AE$2:$AE$60,MATCH(ROWS($A$28:$A37),Matriz!$AH$2:$AH$60,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="27">
         <f>IFERROR(INDEX(Matriz!$AF$2:$AF$60,MATCH(ROWS($A$28:$A37),Matriz!$AH$2:$AH$60,0)),"")</f>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="G37" s="28">
         <f t="shared" si="2"/>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="26" t="s">
@@ -7753,7 +7753,7 @@
       <c r="D41" s="26"/>
       <c r="E41" s="27">
         <f>SUM(Matriz!$AI$2:$AI$60)</f>
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
@@ -8251,7 +8251,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="11">
         <v>0</v>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="AE2" s="4">
         <f>IF($C2="","",SUM($F2:$Q2))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF2" s="4">
         <f>IF($C2="","",COUNTIF($R2:$AC2,"http*"))</f>
@@ -8308,15 +8308,15 @@
       </c>
       <c r="AG2" s="4">
         <f>IF($C2="","",$AE2*1000+(1000-$A2))</f>
-        <v>2999</v>
+        <v>3999</v>
       </c>
       <c r="AH2" s="4">
         <f>IF($C2="","",RANK($AG2,$AG$2:$AG$60))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI2" s="4">
         <f>IF($C2="","",MAX(0,$AE2-$AF2))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ2" s="4">
         <f>IF($C2="","",MAX(0,$AF2-$AE2))</f>
@@ -8368,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="11">
         <v>0</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="AE3" s="4">
         <f t="shared" ref="AE3:AE60" si="0">IF($C3="","",SUM($F3:$Q3))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF3" s="4">
         <f t="shared" ref="AF3:AF60" si="1">IF($C3="","",COUNTIF($R3:$AC3,"http*"))</f>
@@ -8425,15 +8425,15 @@
       </c>
       <c r="AG3" s="4">
         <f t="shared" ref="AG3:AG60" si="2">IF($C3="","",$AE3*1000+(1000-$A3))</f>
-        <v>2998</v>
+        <v>3998</v>
       </c>
       <c r="AH3" s="4">
         <f t="shared" ref="AH3:AH60" si="3">IF($C3="","",RANK($AG3,$AG$2:$AG$60))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI3" s="4">
         <f t="shared" ref="AI3:AI60" si="4">IF($C3="","",MAX(0,$AE3-$AF3))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ3" s="4">
         <f t="shared" ref="AJ3:AJ60" si="5">IF($C3="","",MAX(0,$AF3-$AE3))</f>
@@ -8485,7 +8485,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="11">
         <v>0</v>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF4" s="4">
         <f t="shared" si="1"/>
@@ -8542,15 +8542,15 @@
       </c>
       <c r="AG4" s="4">
         <f t="shared" si="2"/>
-        <v>2997</v>
+        <v>3997</v>
       </c>
       <c r="AH4" s="4">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI4" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ4" s="4">
         <f t="shared" si="5"/>
@@ -8602,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="11">
         <v>0</v>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF5" s="4">
         <f t="shared" si="1"/>
@@ -8659,15 +8659,15 @@
       </c>
       <c r="AG5" s="4">
         <f t="shared" si="2"/>
-        <v>2996</v>
+        <v>3996</v>
       </c>
       <c r="AH5" s="4">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI5" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ5" s="4">
         <f t="shared" si="5"/>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="11">
         <v>0</v>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="1"/>
@@ -8776,15 +8776,15 @@
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="2"/>
-        <v>2995</v>
+        <v>3995</v>
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ6" s="4">
         <f t="shared" si="5"/>
@@ -8836,7 +8836,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="11">
         <v>0</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="1"/>
@@ -8893,15 +8893,15 @@
       </c>
       <c r="AG7" s="4">
         <f t="shared" si="2"/>
-        <v>2994</v>
+        <v>3994</v>
       </c>
       <c r="AH7" s="4">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ7" s="4">
         <f t="shared" si="5"/>
@@ -8953,7 +8953,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="11">
         <v>0</v>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AE8" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF8" s="4">
         <f t="shared" si="1"/>
@@ -9010,15 +9010,15 @@
       </c>
       <c r="AG8" s="4">
         <f t="shared" si="2"/>
-        <v>2993</v>
+        <v>3993</v>
       </c>
       <c r="AH8" s="4">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI8" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ8" s="4">
         <f t="shared" si="5"/>
@@ -9070,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="11">
         <v>0</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AE9" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF9" s="4">
         <f t="shared" si="1"/>
@@ -9127,15 +9127,15 @@
       </c>
       <c r="AG9" s="4">
         <f t="shared" si="2"/>
-        <v>2992</v>
+        <v>3992</v>
       </c>
       <c r="AH9" s="4">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI9" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ9" s="4">
         <f t="shared" si="5"/>
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="11">
         <v>0</v>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="AE10" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF10" s="4">
         <f t="shared" si="1"/>
@@ -9244,15 +9244,15 @@
       </c>
       <c r="AG10" s="4">
         <f t="shared" si="2"/>
-        <v>2991</v>
+        <v>3991</v>
       </c>
       <c r="AH10" s="4">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI10" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ10" s="4">
         <f t="shared" si="5"/>
@@ -9304,7 +9304,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="11">
         <v>0</v>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AE11" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" si="1"/>
@@ -9361,15 +9361,15 @@
       </c>
       <c r="AG11" s="4">
         <f t="shared" si="2"/>
-        <v>2990</v>
+        <v>3990</v>
       </c>
       <c r="AH11" s="4">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ11" s="4">
         <f t="shared" si="5"/>
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="11">
         <v>0</v>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AE12" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="1"/>
@@ -9478,15 +9478,15 @@
       </c>
       <c r="AG12" s="4">
         <f t="shared" si="2"/>
-        <v>2989</v>
+        <v>3989</v>
       </c>
       <c r="AH12" s="4">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ12" s="4">
         <f t="shared" si="5"/>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="11">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AE13" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="1"/>
@@ -9595,15 +9595,15 @@
       </c>
       <c r="AG13" s="4">
         <f t="shared" si="2"/>
-        <v>2988</v>
+        <v>3988</v>
       </c>
       <c r="AH13" s="4">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ13" s="4">
         <f t="shared" si="5"/>
@@ -9655,7 +9655,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="11">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AE14" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="1"/>
@@ -9712,15 +9712,15 @@
       </c>
       <c r="AG14" s="4">
         <f t="shared" si="2"/>
-        <v>2987</v>
+        <v>3987</v>
       </c>
       <c r="AH14" s="4">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ14" s="4">
         <f t="shared" si="5"/>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="11">
         <v>0</v>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="AE15" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="1"/>
@@ -9829,15 +9829,15 @@
       </c>
       <c r="AG15" s="4">
         <f t="shared" si="2"/>
-        <v>2986</v>
+        <v>3986</v>
       </c>
       <c r="AH15" s="4">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ15" s="4">
         <f t="shared" si="5"/>
@@ -9889,7 +9889,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="11">
         <v>0</v>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="AE16" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="1"/>
@@ -9946,15 +9946,15 @@
       </c>
       <c r="AG16" s="4">
         <f t="shared" si="2"/>
-        <v>2985</v>
+        <v>3985</v>
       </c>
       <c r="AH16" s="4">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ16" s="4">
         <f t="shared" si="5"/>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AH18" s="4">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="4"/>
@@ -10240,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="11">
         <v>0</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="AE19" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="1"/>
@@ -10297,15 +10297,15 @@
       </c>
       <c r="AG19" s="4">
         <f t="shared" si="2"/>
-        <v>2982</v>
+        <v>3982</v>
       </c>
       <c r="AH19" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ19" s="4">
         <f t="shared" si="5"/>
@@ -10357,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="11">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AE20" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="1"/>
@@ -10414,15 +10414,15 @@
       </c>
       <c r="AG20" s="4">
         <f t="shared" si="2"/>
-        <v>2981</v>
+        <v>3981</v>
       </c>
       <c r="AH20" s="4">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ20" s="4">
         <f t="shared" si="5"/>
@@ -10474,7 +10474,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="11">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="AE21" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="1"/>
@@ -10531,15 +10531,15 @@
       </c>
       <c r="AG21" s="4">
         <f t="shared" si="2"/>
-        <v>2980</v>
+        <v>3980</v>
       </c>
       <c r="AH21" s="4">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ21" s="4">
         <f t="shared" si="5"/>
@@ -10591,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="11">
         <v>0</v>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="AE22" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="1"/>
@@ -10648,15 +10648,15 @@
       </c>
       <c r="AG22" s="4">
         <f t="shared" si="2"/>
-        <v>2979</v>
+        <v>3979</v>
       </c>
       <c r="AH22" s="4">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ22" s="4">
         <f t="shared" si="5"/>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="11">
         <v>0</v>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AE23" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="1"/>
@@ -10765,15 +10765,15 @@
       </c>
       <c r="AG23" s="4">
         <f t="shared" si="2"/>
-        <v>2978</v>
+        <v>3978</v>
       </c>
       <c r="AH23" s="4">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ23" s="4">
         <f t="shared" si="5"/>
@@ -10825,7 +10825,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="11">
         <v>0</v>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="AE24" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="1"/>
@@ -10882,15 +10882,15 @@
       </c>
       <c r="AG24" s="4">
         <f t="shared" si="2"/>
-        <v>2977</v>
+        <v>3977</v>
       </c>
       <c r="AH24" s="4">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ24" s="4">
         <f t="shared" si="5"/>
@@ -10942,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="11">
         <v>0</v>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="AE25" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="1"/>
@@ -10999,15 +10999,15 @@
       </c>
       <c r="AG25" s="4">
         <f t="shared" si="2"/>
-        <v>2976</v>
+        <v>3976</v>
       </c>
       <c r="AH25" s="4">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ25" s="4">
         <f t="shared" si="5"/>
@@ -11059,7 +11059,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="11">
         <v>0</v>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="AE26" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="1"/>
@@ -11116,15 +11116,15 @@
       </c>
       <c r="AG26" s="4">
         <f t="shared" si="2"/>
-        <v>2975</v>
+        <v>3975</v>
       </c>
       <c r="AH26" s="4">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ26" s="4">
         <f t="shared" si="5"/>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="11">
         <v>0</v>
@@ -11196,7 +11196,7 @@
       <c r="T27" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="U27" s="14" t="s">
+      <c r="U27" s="13" t="s">
         <v>993</v>
       </c>
       <c r="V27" s="14" t="s">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="AE27" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="1"/>
@@ -11233,15 +11233,15 @@
       </c>
       <c r="AG27" s="4">
         <f t="shared" si="2"/>
-        <v>2974</v>
+        <v>3974</v>
       </c>
       <c r="AH27" s="4">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ27" s="4">
         <f t="shared" si="5"/>
@@ -11293,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="11">
         <v>0</v>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="AE28" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="1"/>
@@ -11350,15 +11350,15 @@
       </c>
       <c r="AG28" s="4">
         <f t="shared" si="2"/>
-        <v>2973</v>
+        <v>3973</v>
       </c>
       <c r="AH28" s="4">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ28" s="4">
         <f t="shared" si="5"/>
@@ -11410,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="11">
         <v>0</v>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="AE29" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="1"/>
@@ -11467,15 +11467,15 @@
       </c>
       <c r="AG29" s="4">
         <f t="shared" si="2"/>
-        <v>2972</v>
+        <v>3972</v>
       </c>
       <c r="AH29" s="4">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ29" s="4">
         <f t="shared" si="5"/>
@@ -11527,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="11">
         <v>0</v>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="AE30" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="1"/>
@@ -11584,15 +11584,15 @@
       </c>
       <c r="AG30" s="4">
         <f t="shared" si="2"/>
-        <v>2971</v>
+        <v>3971</v>
       </c>
       <c r="AH30" s="4">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ30" s="4">
         <f t="shared" si="5"/>
@@ -11644,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="11">
         <v>0</v>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="AE31" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="1"/>
@@ -11701,15 +11701,15 @@
       </c>
       <c r="AG31" s="4">
         <f t="shared" si="2"/>
-        <v>2970</v>
+        <v>3970</v>
       </c>
       <c r="AH31" s="4">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ31" s="4">
         <f t="shared" si="5"/>
@@ -11761,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="11">
         <v>0</v>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="AE32" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="1"/>
@@ -11818,15 +11818,15 @@
       </c>
       <c r="AG32" s="4">
         <f t="shared" si="2"/>
-        <v>2969</v>
+        <v>3969</v>
       </c>
       <c r="AH32" s="4">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ32" s="4">
         <f t="shared" si="5"/>
@@ -11878,7 +11878,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="11">
         <v>0</v>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="AE33" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="1"/>
@@ -11935,15 +11935,15 @@
       </c>
       <c r="AG33" s="4">
         <f t="shared" si="2"/>
-        <v>2968</v>
+        <v>3968</v>
       </c>
       <c r="AH33" s="4">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AI33" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" s="4">
         <f t="shared" si="5"/>
@@ -11995,7 +11995,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="11">
         <v>0</v>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="AE34" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF34" s="4">
         <f t="shared" si="1"/>
@@ -12052,15 +12052,15 @@
       </c>
       <c r="AG34" s="4">
         <f t="shared" si="2"/>
-        <v>2967</v>
+        <v>3967</v>
       </c>
       <c r="AH34" s="4">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AI34" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ34" s="4">
         <f t="shared" si="5"/>
@@ -12112,7 +12112,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="11">
         <v>0</v>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="AE35" s="4">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF35" s="4">
         <f t="shared" si="1"/>
@@ -12169,15 +12169,15 @@
       </c>
       <c r="AG35" s="4">
         <f t="shared" si="2"/>
-        <v>4966</v>
+        <v>5966</v>
       </c>
       <c r="AH35" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI35" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ35" s="4">
         <f t="shared" si="5"/>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="11">
         <v>0</v>
@@ -12249,7 +12249,7 @@
       <c r="T36" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="U36" s="14" t="s">
+      <c r="U36" s="13" t="s">
         <v>953</v>
       </c>
       <c r="V36" s="14" t="s">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="AE36" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="1"/>
@@ -12286,15 +12286,15 @@
       </c>
       <c r="AG36" s="4">
         <f t="shared" si="2"/>
-        <v>2965</v>
+        <v>3965</v>
       </c>
       <c r="AH36" s="4">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ36" s="4">
         <f t="shared" si="5"/>
@@ -12346,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="11">
         <v>0</v>
@@ -12366,7 +12366,7 @@
       <c r="T37" s="14" t="s">
         <v>1083</v>
       </c>
-      <c r="U37" s="14" t="s">
+      <c r="U37" s="13" t="s">
         <v>959</v>
       </c>
       <c r="V37" s="14" t="s">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="AE37" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="1"/>
@@ -12403,15 +12403,15 @@
       </c>
       <c r="AG37" s="4">
         <f t="shared" si="2"/>
-        <v>2964</v>
+        <v>3964</v>
       </c>
       <c r="AH37" s="4">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ37" s="4">
         <f t="shared" si="5"/>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="AH38" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="4"/>
@@ -13165,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="11">
         <v>0</v>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="AE44" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="1"/>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AG44" s="4">
         <f t="shared" si="2"/>
-        <v>2957</v>
+        <v>3957</v>
       </c>
       <c r="AH44" s="4">
         <f t="shared" si="3"/>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ44" s="4">
         <f t="shared" si="5"/>
@@ -13282,7 +13282,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="11">
         <v>0</v>
@@ -13331,7 +13331,7 @@
       </c>
       <c r="AE45" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="1"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="AG45" s="4">
         <f t="shared" si="2"/>
-        <v>2956</v>
+        <v>3956</v>
       </c>
       <c r="AH45" s="4">
         <f t="shared" si="3"/>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ45" s="4">
         <f t="shared" si="5"/>
@@ -13399,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="11">
         <v>0</v>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="AE46" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="1"/>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="AG46" s="4">
         <f t="shared" si="2"/>
-        <v>2955</v>
+        <v>3955</v>
       </c>
       <c r="AH46" s="4">
         <f t="shared" si="3"/>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ46" s="4">
         <f t="shared" si="5"/>
@@ -13516,7 +13516,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="11">
         <v>0</v>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="AE47" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF47" s="4">
         <f t="shared" si="1"/>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="AG47" s="4">
         <f t="shared" si="2"/>
-        <v>2954</v>
+        <v>3954</v>
       </c>
       <c r="AH47" s="4">
         <f t="shared" si="3"/>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="AI47" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ47" s="4">
         <f t="shared" si="5"/>
@@ -13633,7 +13633,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="11">
         <v>0</v>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="AE48" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF48" s="4">
         <f t="shared" si="1"/>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="AG48" s="4">
         <f t="shared" si="2"/>
-        <v>2953</v>
+        <v>3953</v>
       </c>
       <c r="AH48" s="4">
         <f t="shared" si="3"/>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="AI48" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ48" s="4">
         <f t="shared" si="5"/>
@@ -15042,7 +15042,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC48" xr:uid="{B93DC578-2EEA-48CF-9EFD-E294C2F4F9E2}"/>
+  <autoFilter ref="A1:AC60" xr:uid="{B93DC578-2EEA-48CF-9EFD-E294C2F4F9E2}"/>
   <conditionalFormatting sqref="F2:Q60">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
@@ -15063,6 +15063,9 @@
     <hyperlink ref="U35" r:id="rId9" xr:uid="{B6ED1C37-5C44-45F0-8AE7-720FBF9292F0}"/>
     <hyperlink ref="W35" r:id="rId10" xr:uid="{5ADC2036-8BE3-4C29-9211-776990B2FA5B}"/>
     <hyperlink ref="X35" r:id="rId11" xr:uid="{7B97F0CB-76D2-4A95-B897-486B43CC99C3}"/>
+    <hyperlink ref="U36" r:id="rId12" xr:uid="{DF184A4C-9F2F-4229-9F82-3F35CBDD176E}"/>
+    <hyperlink ref="U27" r:id="rId13" xr:uid="{DF6FD916-2B24-420E-990D-94436596B42E}"/>
+    <hyperlink ref="U37" r:id="rId14" xr:uid="{BE088A72-E804-4614-B45B-75F0312D7442}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/videos/organization.xlsx
+++ b/videos/organization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/videos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="914" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20323B6F-6C3F-4A48-B8B1-71F4FF39C15E}"/>
+  <xr:revisionPtr revIDLastSave="915" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14FC115B-3DD4-4831-8CD8-89985C4B04CE}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12474,7 +12474,7 @@
       <c r="Q38" s="11">
         <v>0</v>
       </c>
-      <c r="R38" s="14" t="s">
+      <c r="R38" s="13" t="s">
         <v>33</v>
       </c>
       <c r="S38" s="14" t="s">
@@ -15066,6 +15066,7 @@
     <hyperlink ref="U36" r:id="rId12" xr:uid="{DF184A4C-9F2F-4229-9F82-3F35CBDD176E}"/>
     <hyperlink ref="U27" r:id="rId13" xr:uid="{DF6FD916-2B24-420E-990D-94436596B42E}"/>
     <hyperlink ref="U37" r:id="rId14" xr:uid="{BE088A72-E804-4614-B45B-75F0312D7442}"/>
+    <hyperlink ref="R38" r:id="rId15" xr:uid="{47028179-0115-4C3E-8631-AF2E77A56AE9}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
